--- a/data/infant_childcare_facility/data.xlsx
+++ b/data/infant_childcare_facility/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -460,7 +460,7 @@
         <v>087-865-3111</v>
       </c>
       <c r="G2" t="str">
-        <v>http://www.tobiume-shounika.com/program.html</v>
+        <v>https://www.tobiume-shounika.jp/</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -472,7 +472,7 @@
         <v>08:00</v>
       </c>
       <c r="K2" t="str">
-        <v>17:00</v>
+        <v>18:00</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -542,7 +542,7 @@
         <v>087-844-8156</v>
       </c>
       <c r="G4" t="str">
-        <v>https://koba-yashima-clinic.com/%e3%81%99%e3%81%93%e3%82%84%e3%81%8b%e3%83%ab%e3%83%bc%e3%83%a0</v>
+        <v>https://koba-yashima-clinic.com/</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -686,9 +686,47 @@
         <v>月～金は2,000円（3,000円）※（　）内は、本市以外に住所を有する児童の利用料金</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>34.28207</v>
+      </c>
+      <c r="C8" t="str">
+        <v>134.04742</v>
+      </c>
+      <c r="D8" t="str">
+        <v>医療法人社団恵生会いきなりキッズクリニック「たすかるもん」</v>
+      </c>
+      <c r="E8" t="str">
+        <v>高松市内町2-1</v>
+      </c>
+      <c r="F8" t="str">
+        <v>087-813-6220</v>
+      </c>
+      <c r="G8" t="str">
+        <v>https://ikinari-kids.com/</v>
+      </c>
+      <c r="I8" t="str">
+        <v>月火水木金</v>
+      </c>
+      <c r="J8" t="str">
+        <v>08:00</v>
+      </c>
+      <c r="K8" t="str">
+        <v>18:00</v>
+      </c>
+      <c r="L8" t="str">
+        <v>月～金は8:00～18:00</v>
+      </c>
+      <c r="M8" t="str">
+        <v>月～金は2,000円（3,000円）※（　）内は、本市以外に住所を有する児童の利用料金</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M8"/>
   </ignoredErrors>
 </worksheet>
 </file>